--- a/uds_commands_demo.xlsx
+++ b/uds_commands_demo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>FrameType</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>WaitMs</t>
         </is>
       </c>
@@ -498,7 +503,12 @@
           <t>0x50 0x01</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -534,7 +544,12 @@
           <t>0x62 0xF1 0x90</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>100</v>
       </c>
     </row>
@@ -549,26 +564,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0x3E</t>
+          <t>0x19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0x00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>0x02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0xFF</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0x59 0x02 0xFF 0x00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>EXT</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -577,7 +605,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>uploadflashdriver</t>
+          <t>0x3E</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -590,13 +618,18 @@
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>0</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -605,7 +638,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uploadapp</t>
+          <t>uploadflashdriver</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -618,7 +651,45 @@
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x7E0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>uploadapp</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
     </row>
